--- a/artifacts/PLANTILLA_CARGA_MASIVA_v3.xlsx
+++ b/artifacts/PLANTILLA_CARGA_MASIVA_v3.xlsx
@@ -1,13 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B071831-5857-4CED-8F97-E0612CEE192C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Instrucciones" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Carga" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Familias nuevas" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Diagnóstico" state="visible" r:id="rId7"/>
+    <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
+    <sheet name="Carga" sheetId="2" r:id="rId2"/>
+    <sheet name="Familias nuevas" sheetId="3" r:id="rId3"/>
+    <sheet name="Diagnóstico" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -3118,17 +3122,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3492,78 +3498,106 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AD376"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="30" width="20" customWidth="1"/>
+    <col min="1" max="1" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="87.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="46.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3655,7 +3689,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -3747,7 +3781,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -3839,7 +3873,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>48</v>
       </c>
@@ -3931,7 +3965,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -4023,7 +4057,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>54</v>
       </c>
@@ -4115,7 +4149,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -4207,7 +4241,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -4299,7 +4333,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -4391,7 +4425,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>66</v>
       </c>
@@ -4483,7 +4517,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>69</v>
       </c>
@@ -4575,7 +4609,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -4667,7 +4701,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>73</v>
       </c>
@@ -4759,7 +4793,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>75</v>
       </c>
@@ -4851,7 +4885,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>78</v>
       </c>
@@ -4943,7 +4977,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -5035,7 +5069,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>84</v>
       </c>
@@ -5127,7 +5161,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>87</v>
       </c>
@@ -5219,7 +5253,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>89</v>
       </c>
@@ -5311,7 +5345,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>92</v>
       </c>
@@ -5403,7 +5437,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>95</v>
       </c>
@@ -5495,7 +5529,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>97</v>
       </c>
@@ -5587,7 +5621,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>99</v>
       </c>
@@ -5679,7 +5713,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>101</v>
       </c>
@@ -5771,7 +5805,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>103</v>
       </c>
@@ -5863,7 +5897,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>105</v>
       </c>
@@ -5955,7 +5989,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>107</v>
       </c>
@@ -6047,7 +6081,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>110</v>
       </c>
@@ -6139,7 +6173,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>112</v>
       </c>
@@ -6231,7 +6265,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>114</v>
       </c>
@@ -6323,7 +6357,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>116</v>
       </c>
@@ -6415,7 +6449,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>118</v>
       </c>
@@ -6507,7 +6541,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>121</v>
       </c>
@@ -6599,7 +6633,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>123</v>
       </c>
@@ -6691,7 +6725,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>125</v>
       </c>
@@ -6783,7 +6817,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>128</v>
       </c>
@@ -6875,7 +6909,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>130</v>
       </c>
@@ -6967,7 +7001,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>131</v>
       </c>
@@ -7059,7 +7093,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>133</v>
       </c>
@@ -7151,7 +7185,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>135</v>
       </c>
@@ -7243,7 +7277,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>138</v>
       </c>
@@ -7335,7 +7369,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>140</v>
       </c>
@@ -7427,7 +7461,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>141</v>
       </c>
@@ -7519,7 +7553,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>143</v>
       </c>
@@ -7611,7 +7645,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>145</v>
       </c>
@@ -7703,7 +7737,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>148</v>
       </c>
@@ -7795,7 +7829,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>150</v>
       </c>
@@ -7887,7 +7921,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>152</v>
       </c>
@@ -7979,7 +8013,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>154</v>
       </c>
@@ -8071,7 +8105,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>156</v>
       </c>
@@ -8163,7 +8197,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>158</v>
       </c>
@@ -8255,7 +8289,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>160</v>
       </c>
@@ -8347,7 +8381,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>162</v>
       </c>
@@ -8439,7 +8473,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>165</v>
       </c>
@@ -8531,7 +8565,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>167</v>
       </c>
@@ -8623,7 +8657,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>169</v>
       </c>
@@ -8715,7 +8749,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>171</v>
       </c>
@@ -8807,7 +8841,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>173</v>
       </c>
@@ -8899,7 +8933,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>175</v>
       </c>
@@ -8991,7 +9025,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>177</v>
       </c>
@@ -9083,7 +9117,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>179</v>
       </c>
@@ -9175,7 +9209,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>181</v>
       </c>
@@ -9267,7 +9301,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>183</v>
       </c>
@@ -9359,7 +9393,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>186</v>
       </c>
@@ -9451,7 +9485,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>188</v>
       </c>
@@ -9543,7 +9577,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>190</v>
       </c>
@@ -9635,7 +9669,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>192</v>
       </c>
@@ -9727,7 +9761,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>194</v>
       </c>
@@ -9819,7 +9853,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>197</v>
       </c>
@@ -9911,7 +9945,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>199</v>
       </c>
@@ -10003,7 +10037,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>201</v>
       </c>
@@ -10095,7 +10129,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>203</v>
       </c>
@@ -10187,7 +10221,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>205</v>
       </c>
@@ -10279,7 +10313,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>207</v>
       </c>
@@ -10371,7 +10405,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>209</v>
       </c>
@@ -10463,7 +10497,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>211</v>
       </c>
@@ -10555,7 +10589,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>213</v>
       </c>
@@ -10647,7 +10681,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>215</v>
       </c>
@@ -10739,7 +10773,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>217</v>
       </c>
@@ -10831,7 +10865,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>219</v>
       </c>
@@ -10923,7 +10957,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="81" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>221</v>
       </c>
@@ -11015,7 +11049,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="82" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>223</v>
       </c>
@@ -11107,7 +11141,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="83" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>225</v>
       </c>
@@ -11199,7 +11233,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="84" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>227</v>
       </c>
@@ -11291,7 +11325,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="85" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>229</v>
       </c>
@@ -11383,7 +11417,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="86" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>231</v>
       </c>
@@ -11475,7 +11509,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="87" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>233</v>
       </c>
@@ -11567,7 +11601,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="88" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>235</v>
       </c>
@@ -11659,7 +11693,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="89" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>237</v>
       </c>
@@ -11751,7 +11785,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="90" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>239</v>
       </c>
@@ -11843,7 +11877,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="91" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>241</v>
       </c>
@@ -11935,7 +11969,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="92" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>243</v>
       </c>
@@ -12027,7 +12061,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="93" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>245</v>
       </c>
@@ -12119,7 +12153,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="94" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>247</v>
       </c>
@@ -12211,7 +12245,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="95" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>249</v>
       </c>
@@ -12303,7 +12337,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="96" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>251</v>
       </c>
@@ -12395,7 +12429,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>253</v>
       </c>
@@ -12487,7 +12521,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>255</v>
       </c>
@@ -12579,7 +12613,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>257</v>
       </c>
@@ -12671,7 +12705,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>259</v>
       </c>
@@ -12763,7 +12797,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>261</v>
       </c>
@@ -12855,7 +12889,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>263</v>
       </c>
@@ -12947,7 +12981,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>265</v>
       </c>
@@ -13039,7 +13073,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>267</v>
       </c>
@@ -13131,7 +13165,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>269</v>
       </c>
@@ -13223,7 +13257,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>271</v>
       </c>
@@ -13315,7 +13349,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>273</v>
       </c>
@@ -13407,7 +13441,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>275</v>
       </c>
@@ -13499,7 +13533,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="109" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>277</v>
       </c>
@@ -13591,7 +13625,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>279</v>
       </c>
@@ -13683,7 +13717,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>281</v>
       </c>
@@ -13775,7 +13809,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>283</v>
       </c>
@@ -13867,7 +13901,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="113" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>285</v>
       </c>
@@ -13959,7 +13993,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="114" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>287</v>
       </c>
@@ -14051,7 +14085,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="115" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>289</v>
       </c>
@@ -14143,7 +14177,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="116" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>291</v>
       </c>
@@ -14235,7 +14269,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="117" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>293</v>
       </c>
@@ -14327,7 +14361,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="118" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>295</v>
       </c>
@@ -14419,7 +14453,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="119" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>297</v>
       </c>
@@ -14511,7 +14545,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="120" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>299</v>
       </c>
@@ -14603,7 +14637,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="121" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>301</v>
       </c>
@@ -14695,7 +14729,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="122" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>303</v>
       </c>
@@ -14787,7 +14821,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="123" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>305</v>
       </c>
@@ -14879,7 +14913,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="124" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>307</v>
       </c>
@@ -14971,7 +15005,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="125" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>309</v>
       </c>
@@ -15063,7 +15097,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="126" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>311</v>
       </c>
@@ -15155,7 +15189,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="127" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>313</v>
       </c>
@@ -15247,7 +15281,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="128" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>315</v>
       </c>
@@ -15339,7 +15373,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="129" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>317</v>
       </c>
@@ -15431,7 +15465,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="130" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>319</v>
       </c>
@@ -15523,7 +15557,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="131" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>321</v>
       </c>
@@ -15615,7 +15649,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="132" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>323</v>
       </c>
@@ -15707,7 +15741,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="133" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>325</v>
       </c>
@@ -15799,7 +15833,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="134" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>327</v>
       </c>
@@ -15891,7 +15925,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="135" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>329</v>
       </c>
@@ -15983,7 +16017,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="136" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>331</v>
       </c>
@@ -16075,7 +16109,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="137" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>333</v>
       </c>
@@ -16167,7 +16201,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="138" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>335</v>
       </c>
@@ -16259,7 +16293,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="139" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>337</v>
       </c>
@@ -16351,7 +16385,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="140" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>339</v>
       </c>
@@ -16443,7 +16477,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="141" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>341</v>
       </c>
@@ -16535,7 +16569,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="142" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>343</v>
       </c>
@@ -16627,7 +16661,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="143" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>345</v>
       </c>
@@ -16719,7 +16753,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="144" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>347</v>
       </c>
@@ -16811,7 +16845,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="145" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>349</v>
       </c>
@@ -16903,7 +16937,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="146" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>351</v>
       </c>
@@ -16995,7 +17029,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="147" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>353</v>
       </c>
@@ -17087,7 +17121,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="148" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>355</v>
       </c>
@@ -17179,7 +17213,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="149" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>357</v>
       </c>
@@ -17271,7 +17305,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="150" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>359</v>
       </c>
@@ -17363,7 +17397,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="151" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>361</v>
       </c>
@@ -17455,7 +17489,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="152" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>363</v>
       </c>
@@ -17547,7 +17581,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="153" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>365</v>
       </c>
@@ -17639,7 +17673,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="154" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>367</v>
       </c>
@@ -17731,7 +17765,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="155" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>369</v>
       </c>
@@ -17823,7 +17857,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="156" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>371</v>
       </c>
@@ -17915,7 +17949,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="157" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>373</v>
       </c>
@@ -18007,7 +18041,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="158" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>375</v>
       </c>
@@ -18099,7 +18133,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="159" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>377</v>
       </c>
@@ -18191,7 +18225,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="160" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>379</v>
       </c>
@@ -18283,7 +18317,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="161" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>381</v>
       </c>
@@ -18375,7 +18409,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="162" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>383</v>
       </c>
@@ -18467,7 +18501,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="163" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>385</v>
       </c>
@@ -18559,7 +18593,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="164" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>387</v>
       </c>
@@ -18651,7 +18685,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="165" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>389</v>
       </c>
@@ -18743,7 +18777,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="166" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>391</v>
       </c>
@@ -18835,7 +18869,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="167" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>393</v>
       </c>
@@ -18927,7 +18961,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="168" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>395</v>
       </c>
@@ -19019,7 +19053,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="169" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>397</v>
       </c>
@@ -19111,7 +19145,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="170" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>399</v>
       </c>
@@ -19203,7 +19237,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="171" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>401</v>
       </c>
@@ -19295,7 +19329,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="172" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>403</v>
       </c>
@@ -19387,7 +19421,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="173" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>405</v>
       </c>
@@ -19479,7 +19513,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="174" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>407</v>
       </c>
@@ -19571,7 +19605,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="175" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>409</v>
       </c>
@@ -19663,7 +19697,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="176" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>411</v>
       </c>
@@ -19755,7 +19789,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="177" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>413</v>
       </c>
@@ -19847,7 +19881,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="178" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>415</v>
       </c>
@@ -19939,7 +19973,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="179" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>417</v>
       </c>
@@ -20031,7 +20065,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="180" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>419</v>
       </c>
@@ -20123,7 +20157,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="181" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>422</v>
       </c>
@@ -20215,7 +20249,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="182" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>425</v>
       </c>
@@ -20307,7 +20341,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="183" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>428</v>
       </c>
@@ -20399,7 +20433,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="184" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>431</v>
       </c>
@@ -20491,7 +20525,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="185" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>433</v>
       </c>
@@ -20583,7 +20617,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="186" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>435</v>
       </c>
@@ -20675,7 +20709,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="187" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>438</v>
       </c>
@@ -20767,7 +20801,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="188" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>440</v>
       </c>
@@ -20859,7 +20893,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="189" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>442</v>
       </c>
@@ -20951,7 +20985,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="190" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>444</v>
       </c>
@@ -21043,7 +21077,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="191" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>446</v>
       </c>
@@ -21135,7 +21169,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="192" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>448</v>
       </c>
@@ -21227,7 +21261,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="193" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>450</v>
       </c>
@@ -21319,7 +21353,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="194" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>452</v>
       </c>
@@ -21411,7 +21445,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="195" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>454</v>
       </c>
@@ -21503,7 +21537,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="196" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>456</v>
       </c>
@@ -21595,7 +21629,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="197" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>458</v>
       </c>
@@ -21687,7 +21721,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="198" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>460</v>
       </c>
@@ -21779,7 +21813,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="199" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>462</v>
       </c>
@@ -21871,7 +21905,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="200" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>464</v>
       </c>
@@ -21963,7 +21997,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="201" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>466</v>
       </c>
@@ -22055,7 +22089,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="202" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>468</v>
       </c>
@@ -22147,7 +22181,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="203" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>470</v>
       </c>
@@ -22239,7 +22273,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="204" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>472</v>
       </c>
@@ -22331,7 +22365,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="205" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>474</v>
       </c>
@@ -22423,7 +22457,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="206" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>476</v>
       </c>
@@ -22515,7 +22549,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="207" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>478</v>
       </c>
@@ -22607,7 +22641,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="208" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>480</v>
       </c>
@@ -22699,7 +22733,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="209" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>482</v>
       </c>
@@ -22791,7 +22825,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="210" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>484</v>
       </c>
@@ -22883,7 +22917,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="211" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>486</v>
       </c>
@@ -22975,7 +23009,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="212" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>488</v>
       </c>
@@ -23067,7 +23101,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="213" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>490</v>
       </c>
@@ -23159,7 +23193,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="214" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>492</v>
       </c>
@@ -23251,7 +23285,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="215" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>494</v>
       </c>
@@ -23343,7 +23377,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="216" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>496</v>
       </c>
@@ -23435,7 +23469,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="217" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>498</v>
       </c>
@@ -23527,7 +23561,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="218" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>500</v>
       </c>
@@ -23619,7 +23653,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="219" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>502</v>
       </c>
@@ -23711,7 +23745,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="220" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>504</v>
       </c>
@@ -23803,7 +23837,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="221" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>506</v>
       </c>
@@ -23895,7 +23929,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="222" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>508</v>
       </c>
@@ -23987,7 +24021,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="223" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>510</v>
       </c>
@@ -24079,7 +24113,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="224" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>512</v>
       </c>
@@ -24171,7 +24205,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="225" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>514</v>
       </c>
@@ -24263,7 +24297,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="226" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>516</v>
       </c>
@@ -24355,7 +24389,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="227" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>518</v>
       </c>
@@ -24447,7 +24481,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="228" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>520</v>
       </c>
@@ -24539,7 +24573,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="229" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>522</v>
       </c>
@@ -24631,7 +24665,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="230" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>524</v>
       </c>
@@ -24723,7 +24757,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="231" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>526</v>
       </c>
@@ -24815,7 +24849,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="232" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>528</v>
       </c>
@@ -24907,7 +24941,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="233" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>530</v>
       </c>
@@ -24999,7 +25033,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="234" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>532</v>
       </c>
@@ -25091,7 +25125,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="235" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>534</v>
       </c>
@@ -25183,7 +25217,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="236" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>536</v>
       </c>
@@ -25275,7 +25309,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="237" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>538</v>
       </c>
@@ -25367,7 +25401,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="238" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>540</v>
       </c>
@@ -25459,7 +25493,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="239" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>542</v>
       </c>
@@ -25551,7 +25585,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="240" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>544</v>
       </c>
@@ -25643,7 +25677,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="241" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>546</v>
       </c>
@@ -25735,7 +25769,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="242" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>548</v>
       </c>
@@ -25827,7 +25861,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="243" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>550</v>
       </c>
@@ -25919,7 +25953,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="244" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>552</v>
       </c>
@@ -26011,7 +26045,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="245" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>554</v>
       </c>
@@ -26103,7 +26137,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="246" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>556</v>
       </c>
@@ -26195,7 +26229,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="247" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>558</v>
       </c>
@@ -26287,7 +26321,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="248" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>560</v>
       </c>
@@ -26379,7 +26413,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="249" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>562</v>
       </c>
@@ -26471,7 +26505,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="250" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>564</v>
       </c>
@@ -26563,7 +26597,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="251" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>566</v>
       </c>
@@ -26655,7 +26689,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="252" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>568</v>
       </c>
@@ -26747,7 +26781,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="253" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>570</v>
       </c>
@@ -26839,7 +26873,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="254" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>572</v>
       </c>
@@ -26931,7 +26965,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="255" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>574</v>
       </c>
@@ -27023,7 +27057,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="256" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>576</v>
       </c>
@@ -27115,7 +27149,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="257" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>578</v>
       </c>
@@ -27207,7 +27241,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="258" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>580</v>
       </c>
@@ -27299,7 +27333,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="259" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>582</v>
       </c>
@@ -27391,7 +27425,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="260" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>584</v>
       </c>
@@ -27483,7 +27517,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="261" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>586</v>
       </c>
@@ -27575,7 +27609,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="262" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>588</v>
       </c>
@@ -27667,7 +27701,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="263" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>590</v>
       </c>
@@ -27759,7 +27793,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="264" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>592</v>
       </c>
@@ -27851,7 +27885,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="265" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>594</v>
       </c>
@@ -27943,7 +27977,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="266" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>596</v>
       </c>
@@ -28035,7 +28069,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="267" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>598</v>
       </c>
@@ -28127,7 +28161,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="268" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>600</v>
       </c>
@@ -28219,7 +28253,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="269" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>602</v>
       </c>
@@ -28311,7 +28345,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="270" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>605</v>
       </c>
@@ -28403,7 +28437,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="271" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>608</v>
       </c>
@@ -28495,7 +28529,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="272" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>611</v>
       </c>
@@ -28587,7 +28621,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="273" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>613</v>
       </c>
@@ -28679,7 +28713,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="274" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>615</v>
       </c>
@@ -28771,7 +28805,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="275" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>617</v>
       </c>
@@ -28863,7 +28897,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="276" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>619</v>
       </c>
@@ -28955,7 +28989,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="277" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>621</v>
       </c>
@@ -29047,7 +29081,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="278" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>623</v>
       </c>
@@ -29139,7 +29173,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="279" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>625</v>
       </c>
@@ -29231,7 +29265,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="280" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>627</v>
       </c>
@@ -29323,7 +29357,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="281" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>629</v>
       </c>
@@ -29415,7 +29449,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="282" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>631</v>
       </c>
@@ -29507,7 +29541,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="283" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>633</v>
       </c>
@@ -29599,7 +29633,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="284" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>635</v>
       </c>
@@ -29691,7 +29725,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="285" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>637</v>
       </c>
@@ -29783,7 +29817,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="286" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>639</v>
       </c>
@@ -29875,7 +29909,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="287" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>641</v>
       </c>
@@ -29967,7 +30001,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="288" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>643</v>
       </c>
@@ -30059,7 +30093,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="289" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>646</v>
       </c>
@@ -30151,7 +30185,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="290" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>648</v>
       </c>
@@ -30243,7 +30277,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="291" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>651</v>
       </c>
@@ -30335,7 +30369,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="292" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>653</v>
       </c>
@@ -30427,7 +30461,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="293" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>656</v>
       </c>
@@ -30519,7 +30553,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="294" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>658</v>
       </c>
@@ -30611,7 +30645,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="295" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>660</v>
       </c>
@@ -30703,7 +30737,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="296" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>662</v>
       </c>
@@ -30795,7 +30829,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="297" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>665</v>
       </c>
@@ -30887,7 +30921,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="298" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>667</v>
       </c>
@@ -30979,7 +31013,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="299" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>670</v>
       </c>
@@ -31071,7 +31105,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="300" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>672</v>
       </c>
@@ -31163,7 +31197,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="301" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>674</v>
       </c>
@@ -31255,7 +31289,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="302" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>676</v>
       </c>
@@ -31347,7 +31381,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="303" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>678</v>
       </c>
@@ -31439,7 +31473,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="304" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>680</v>
       </c>
@@ -31531,7 +31565,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="305" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>682</v>
       </c>
@@ -31623,7 +31657,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="306" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>684</v>
       </c>
@@ -31715,7 +31749,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="307" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>686</v>
       </c>
@@ -31807,7 +31841,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="308" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>688</v>
       </c>
@@ -31899,7 +31933,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="309" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>690</v>
       </c>
@@ -31991,7 +32025,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="310" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>692</v>
       </c>
@@ -32083,7 +32117,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="311" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>694</v>
       </c>
@@ -32175,7 +32209,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="312" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>696</v>
       </c>
@@ -32267,7 +32301,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="313" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>698</v>
       </c>
@@ -32359,7 +32393,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="314" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>699</v>
       </c>
@@ -32451,7 +32485,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="315" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>702</v>
       </c>
@@ -32543,7 +32577,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="316" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>704</v>
       </c>
@@ -32635,7 +32669,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="317" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>706</v>
       </c>
@@ -32727,7 +32761,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="318" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>709</v>
       </c>
@@ -32819,7 +32853,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="319" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>711</v>
       </c>
@@ -32911,7 +32945,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="320" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>713</v>
       </c>
@@ -33003,7 +33037,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="321" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>716</v>
       </c>
@@ -33095,7 +33129,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="322" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>718</v>
       </c>
@@ -33187,7 +33221,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="323" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>720</v>
       </c>
@@ -33279,7 +33313,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="324" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>722</v>
       </c>
@@ -33371,7 +33405,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="325" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>724</v>
       </c>
@@ -33463,7 +33497,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="326" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>726</v>
       </c>
@@ -33555,7 +33589,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="327" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>728</v>
       </c>
@@ -33647,7 +33681,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="328" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>730</v>
       </c>
@@ -33739,7 +33773,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="329" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>732</v>
       </c>
@@ -33831,7 +33865,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="330" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>734</v>
       </c>
@@ -33923,7 +33957,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="331" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>736</v>
       </c>
@@ -34015,7 +34049,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="332" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>738</v>
       </c>
@@ -34107,7 +34141,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="333" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>740</v>
       </c>
@@ -34199,7 +34233,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="334" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>742</v>
       </c>
@@ -34291,7 +34325,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="335" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>744</v>
       </c>
@@ -34383,7 +34417,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="336" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>746</v>
       </c>
@@ -34475,7 +34509,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="337" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>748</v>
       </c>
@@ -34567,7 +34601,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="338" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>751</v>
       </c>
@@ -34659,7 +34693,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="339" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>754</v>
       </c>
@@ -34751,7 +34785,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="340" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>756</v>
       </c>
@@ -34843,7 +34877,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="341" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>758</v>
       </c>
@@ -34935,7 +34969,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="342" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>760</v>
       </c>
@@ -35027,7 +35061,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="343" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>762</v>
       </c>
@@ -35119,7 +35153,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="344" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>765</v>
       </c>
@@ -35211,7 +35245,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="345" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>767</v>
       </c>
@@ -35303,7 +35337,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="346" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>769</v>
       </c>
@@ -35395,7 +35429,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="347" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>771</v>
       </c>
@@ -35487,7 +35521,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="348" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>773</v>
       </c>
@@ -35579,7 +35613,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="349" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>775</v>
       </c>
@@ -35671,7 +35705,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="350" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>777</v>
       </c>
@@ -35763,7 +35797,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="351" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>779</v>
       </c>
@@ -35855,7 +35889,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="352" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>781</v>
       </c>
@@ -35947,7 +35981,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="353" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>783</v>
       </c>
@@ -36039,7 +36073,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="354" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>785</v>
       </c>
@@ -36131,7 +36165,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="355" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>787</v>
       </c>
@@ -36223,7 +36257,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="356" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>789</v>
       </c>
@@ -36315,7 +36349,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="357" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>791</v>
       </c>
@@ -36407,7 +36441,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="358" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>794</v>
       </c>
@@ -36499,7 +36533,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="359" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>795</v>
       </c>
@@ -36591,7 +36625,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="360" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>797</v>
       </c>
@@ -36683,7 +36717,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="361" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>800</v>
       </c>
@@ -36775,7 +36809,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="362" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>802</v>
       </c>
@@ -36867,7 +36901,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="363" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>804</v>
       </c>
@@ -36959,7 +36993,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="364" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>806</v>
       </c>
@@ -37051,7 +37085,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="365" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>809</v>
       </c>
@@ -37143,7 +37177,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="366" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>811</v>
       </c>
@@ -37235,7 +37269,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="367" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>813</v>
       </c>
@@ -37327,7 +37361,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="368" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>816</v>
       </c>
@@ -37419,7 +37453,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="369" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>818</v>
       </c>
@@ -37511,7 +37545,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="370" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>820</v>
       </c>
@@ -37603,7 +37637,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="371" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>822</v>
       </c>
@@ -37695,7 +37729,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="372" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>824</v>
       </c>
@@ -37787,7 +37821,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="373" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>827</v>
       </c>
@@ -37879,7 +37913,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="374" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>829</v>
       </c>
@@ -37971,7 +38005,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="375" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>832</v>
       </c>
@@ -38063,7 +38097,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="376" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>834</v>
       </c>
@@ -38157,19 +38191,19 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="7" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>836</v>
       </c>
@@ -38192,7 +38226,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>842</v>
       </c>
@@ -38215,7 +38249,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>843</v>
       </c>
@@ -38238,7 +38272,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>844</v>
       </c>
@@ -38261,7 +38295,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>845</v>
       </c>
@@ -38284,7 +38318,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>846</v>
       </c>
@@ -38309,19 +38343,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I376"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="9" width="20" customWidth="1"/>
+    <col min="1" max="1" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="9" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -38350,7 +38385,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -38379,7 +38414,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -38408,7 +38443,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>48</v>
       </c>
@@ -38437,7 +38472,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -38466,7 +38501,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>54</v>
       </c>
@@ -38495,7 +38530,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -38524,7 +38559,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -38553,7 +38588,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -38582,7 +38617,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>66</v>
       </c>
@@ -38611,7 +38646,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>69</v>
       </c>
@@ -38640,7 +38675,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -38669,7 +38704,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>73</v>
       </c>
@@ -38698,7 +38733,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>75</v>
       </c>
@@ -38727,7 +38762,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>78</v>
       </c>
@@ -38756,7 +38791,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -38785,7 +38820,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>84</v>
       </c>
@@ -38814,7 +38849,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>87</v>
       </c>
@@ -38843,7 +38878,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>89</v>
       </c>
@@ -38872,7 +38907,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>92</v>
       </c>
@@ -38901,7 +38936,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>95</v>
       </c>
@@ -38930,7 +38965,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>97</v>
       </c>
@@ -38959,7 +38994,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>99</v>
       </c>
@@ -38988,7 +39023,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>101</v>
       </c>
@@ -39017,7 +39052,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>103</v>
       </c>
@@ -39046,7 +39081,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>105</v>
       </c>
@@ -39075,7 +39110,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>107</v>
       </c>
@@ -39104,7 +39139,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>110</v>
       </c>
@@ -39133,7 +39168,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>112</v>
       </c>
@@ -39162,7 +39197,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>114</v>
       </c>
@@ -39191,7 +39226,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>116</v>
       </c>
@@ -39220,7 +39255,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>118</v>
       </c>
@@ -39249,7 +39284,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>121</v>
       </c>
@@ -39278,7 +39313,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>123</v>
       </c>
@@ -39307,7 +39342,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>125</v>
       </c>
@@ -39336,7 +39371,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>128</v>
       </c>
@@ -39365,7 +39400,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>130</v>
       </c>
@@ -39394,7 +39429,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>131</v>
       </c>
@@ -39423,7 +39458,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>133</v>
       </c>
@@ -39452,7 +39487,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>135</v>
       </c>
@@ -39481,7 +39516,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>138</v>
       </c>
@@ -39510,7 +39545,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>140</v>
       </c>
@@ -39539,7 +39574,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>141</v>
       </c>
@@ -39568,7 +39603,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>143</v>
       </c>
@@ -39597,7 +39632,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>145</v>
       </c>
@@ -39626,7 +39661,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>148</v>
       </c>
@@ -39655,7 +39690,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>150</v>
       </c>
@@ -39684,7 +39719,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>152</v>
       </c>
@@ -39713,7 +39748,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>154</v>
       </c>
@@ -39742,7 +39777,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>156</v>
       </c>
@@ -39771,7 +39806,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>158</v>
       </c>
@@ -39800,7 +39835,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>160</v>
       </c>
@@ -39829,7 +39864,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>162</v>
       </c>
@@ -39858,7 +39893,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>165</v>
       </c>
@@ -39887,7 +39922,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>167</v>
       </c>
@@ -39916,7 +39951,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>169</v>
       </c>
@@ -39945,7 +39980,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>171</v>
       </c>
@@ -39974,7 +40009,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>173</v>
       </c>
@@ -40003,7 +40038,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>175</v>
       </c>
@@ -40032,7 +40067,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>177</v>
       </c>
@@ -40061,7 +40096,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>179</v>
       </c>
@@ -40090,7 +40125,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>181</v>
       </c>
@@ -40119,7 +40154,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>183</v>
       </c>
@@ -40148,7 +40183,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>186</v>
       </c>
@@ -40177,7 +40212,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>188</v>
       </c>
@@ -40206,7 +40241,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>190</v>
       </c>
@@ -40235,7 +40270,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>192</v>
       </c>
@@ -40264,7 +40299,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>194</v>
       </c>
@@ -40293,7 +40328,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>197</v>
       </c>
@@ -40322,7 +40357,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>199</v>
       </c>
@@ -40351,7 +40386,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>201</v>
       </c>
@@ -40380,7 +40415,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>203</v>
       </c>
@@ -40409,7 +40444,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>205</v>
       </c>
@@ -40438,7 +40473,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>207</v>
       </c>
@@ -40467,7 +40502,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>209</v>
       </c>
@@ -40496,7 +40531,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>211</v>
       </c>
@@ -40525,7 +40560,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>213</v>
       </c>
@@ -40554,7 +40589,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>215</v>
       </c>
@@ -40583,7 +40618,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>217</v>
       </c>
@@ -40612,7 +40647,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>219</v>
       </c>
@@ -40641,7 +40676,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>221</v>
       </c>
@@ -40670,7 +40705,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>223</v>
       </c>
@@ -40699,7 +40734,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>225</v>
       </c>
@@ -40728,7 +40763,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>227</v>
       </c>
@@ -40757,7 +40792,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>229</v>
       </c>
@@ -40786,7 +40821,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>231</v>
       </c>
@@ -40815,7 +40850,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>233</v>
       </c>
@@ -40844,7 +40879,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>235</v>
       </c>
@@ -40873,7 +40908,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>237</v>
       </c>
@@ -40902,7 +40937,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>239</v>
       </c>
@@ -40931,7 +40966,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>241</v>
       </c>
@@ -40960,7 +40995,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>243</v>
       </c>
@@ -40989,7 +41024,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>245</v>
       </c>
@@ -41018,7 +41053,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>247</v>
       </c>
@@ -41047,7 +41082,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>249</v>
       </c>
@@ -41076,7 +41111,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>251</v>
       </c>
@@ -41105,7 +41140,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>253</v>
       </c>
@@ -41134,7 +41169,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>255</v>
       </c>
@@ -41163,7 +41198,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>257</v>
       </c>
@@ -41192,7 +41227,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>259</v>
       </c>
@@ -41221,7 +41256,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>261</v>
       </c>
@@ -41250,7 +41285,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>263</v>
       </c>
@@ -41279,7 +41314,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>265</v>
       </c>
@@ -41308,7 +41343,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>267</v>
       </c>
@@ -41337,7 +41372,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>269</v>
       </c>
@@ -41366,7 +41401,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>271</v>
       </c>
@@ -41395,7 +41430,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>273</v>
       </c>
@@ -41424,7 +41459,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>275</v>
       </c>
@@ -41453,7 +41488,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>277</v>
       </c>
@@ -41482,7 +41517,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>279</v>
       </c>
@@ -41511,7 +41546,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>281</v>
       </c>
@@ -41540,7 +41575,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>283</v>
       </c>
@@ -41569,7 +41604,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>285</v>
       </c>
@@ -41598,7 +41633,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>287</v>
       </c>
@@ -41627,7 +41662,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>289</v>
       </c>
@@ -41656,7 +41691,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>291</v>
       </c>
@@ -41685,7 +41720,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>293</v>
       </c>
@@ -41714,7 +41749,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>295</v>
       </c>
@@ -41743,7 +41778,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>297</v>
       </c>
@@ -41772,7 +41807,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>299</v>
       </c>
@@ -41801,7 +41836,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>301</v>
       </c>
@@ -41830,7 +41865,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>303</v>
       </c>
@@ -41859,7 +41894,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>305</v>
       </c>
@@ -41888,7 +41923,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>307</v>
       </c>
@@ -41917,7 +41952,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>309</v>
       </c>
@@ -41946,7 +41981,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>311</v>
       </c>
@@ -41975,7 +42010,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>313</v>
       </c>
@@ -42004,7 +42039,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>315</v>
       </c>
@@ -42033,7 +42068,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>317</v>
       </c>
@@ -42062,7 +42097,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>319</v>
       </c>
@@ -42091,7 +42126,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>321</v>
       </c>
@@ -42120,7 +42155,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>323</v>
       </c>
@@ -42149,7 +42184,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>325</v>
       </c>
@@ -42178,7 +42213,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>327</v>
       </c>
@@ -42207,7 +42242,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>329</v>
       </c>
@@ -42236,7 +42271,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>331</v>
       </c>
@@ -42265,7 +42300,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>333</v>
       </c>
@@ -42294,7 +42329,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>335</v>
       </c>
@@ -42323,7 +42358,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>337</v>
       </c>
@@ -42352,7 +42387,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>339</v>
       </c>
@@ -42381,7 +42416,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>341</v>
       </c>
@@ -42410,7 +42445,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>343</v>
       </c>
@@ -42439,7 +42474,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>345</v>
       </c>
@@ -42468,7 +42503,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>347</v>
       </c>
@@ -42497,7 +42532,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>349</v>
       </c>
@@ -42526,7 +42561,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>351</v>
       </c>
@@ -42555,7 +42590,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>353</v>
       </c>
@@ -42584,7 +42619,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>355</v>
       </c>
@@ -42613,7 +42648,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>357</v>
       </c>
@@ -42642,7 +42677,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>359</v>
       </c>
@@ -42671,7 +42706,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>361</v>
       </c>
@@ -42700,7 +42735,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>363</v>
       </c>
@@ -42729,7 +42764,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>365</v>
       </c>
@@ -42758,7 +42793,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>367</v>
       </c>
@@ -42787,7 +42822,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>369</v>
       </c>
@@ -42816,7 +42851,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>371</v>
       </c>
@@ -42845,7 +42880,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>373</v>
       </c>
@@ -42874,7 +42909,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>375</v>
       </c>
@@ -42903,7 +42938,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>377</v>
       </c>
@@ -42932,7 +42967,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>379</v>
       </c>
@@ -42961,7 +42996,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>381</v>
       </c>
@@ -42990,7 +43025,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>383</v>
       </c>
@@ -43019,7 +43054,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>385</v>
       </c>
@@ -43048,7 +43083,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>387</v>
       </c>
@@ -43077,7 +43112,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>389</v>
       </c>
@@ -43106,7 +43141,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>391</v>
       </c>
@@ -43135,7 +43170,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>393</v>
       </c>
@@ -43164,7 +43199,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>395</v>
       </c>
@@ -43193,7 +43228,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>397</v>
       </c>
@@ -43222,7 +43257,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>399</v>
       </c>
@@ -43251,7 +43286,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>401</v>
       </c>
@@ -43280,7 +43315,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>403</v>
       </c>
@@ -43309,7 +43344,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>405</v>
       </c>
@@ -43338,7 +43373,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>407</v>
       </c>
@@ -43367,7 +43402,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>409</v>
       </c>
@@ -43396,7 +43431,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>411</v>
       </c>
@@ -43425,7 +43460,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>413</v>
       </c>
@@ -43454,7 +43489,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>415</v>
       </c>
@@ -43483,7 +43518,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>417</v>
       </c>
@@ -43512,7 +43547,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>419</v>
       </c>
@@ -43541,7 +43576,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>422</v>
       </c>
@@ -43570,7 +43605,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>425</v>
       </c>
@@ -43599,7 +43634,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>428</v>
       </c>
@@ -43628,7 +43663,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>431</v>
       </c>
@@ -43657,7 +43692,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>433</v>
       </c>
@@ -43686,7 +43721,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>435</v>
       </c>
@@ -43715,7 +43750,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>438</v>
       </c>
@@ -43744,7 +43779,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>440</v>
       </c>
@@ -43773,7 +43808,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>442</v>
       </c>
@@ -43802,7 +43837,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>444</v>
       </c>
@@ -43831,7 +43866,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>446</v>
       </c>
@@ -43860,7 +43895,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>448</v>
       </c>
@@ -43889,7 +43924,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>450</v>
       </c>
@@ -43918,7 +43953,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>452</v>
       </c>
@@ -43947,7 +43982,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>454</v>
       </c>
@@ -43976,7 +44011,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>456</v>
       </c>
@@ -44005,7 +44040,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>458</v>
       </c>
@@ -44034,7 +44069,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>460</v>
       </c>
@@ -44063,7 +44098,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>462</v>
       </c>
@@ -44092,7 +44127,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>464</v>
       </c>
@@ -44121,7 +44156,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>466</v>
       </c>
@@ -44150,7 +44185,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>468</v>
       </c>
@@ -44179,7 +44214,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>470</v>
       </c>
@@ -44208,7 +44243,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>472</v>
       </c>
@@ -44237,7 +44272,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>474</v>
       </c>
@@ -44266,7 +44301,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>476</v>
       </c>
@@ -44295,7 +44330,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>478</v>
       </c>
@@ -44324,7 +44359,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>480</v>
       </c>
@@ -44353,7 +44388,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>482</v>
       </c>
@@ -44382,7 +44417,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>484</v>
       </c>
@@ -44411,7 +44446,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>486</v>
       </c>
@@ -44440,7 +44475,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>488</v>
       </c>
@@ -44469,7 +44504,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>490</v>
       </c>
@@ -44498,7 +44533,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>492</v>
       </c>
@@ -44527,7 +44562,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>494</v>
       </c>
@@ -44556,7 +44591,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>496</v>
       </c>
@@ -44585,7 +44620,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>498</v>
       </c>
@@ -44614,7 +44649,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>500</v>
       </c>
@@ -44643,7 +44678,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>502</v>
       </c>
@@ -44672,7 +44707,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>504</v>
       </c>
@@ -44701,7 +44736,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>506</v>
       </c>
@@ -44730,7 +44765,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>508</v>
       </c>
@@ -44759,7 +44794,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>510</v>
       </c>
@@ -44788,7 +44823,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>512</v>
       </c>
@@ -44817,7 +44852,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>514</v>
       </c>
@@ -44846,7 +44881,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>516</v>
       </c>
@@ -44875,7 +44910,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>518</v>
       </c>
@@ -44904,7 +44939,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>520</v>
       </c>
@@ -44933,7 +44968,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>522</v>
       </c>
@@ -44962,7 +44997,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>524</v>
       </c>
@@ -44991,7 +45026,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>526</v>
       </c>
@@ -45020,7 +45055,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>528</v>
       </c>
@@ -45049,7 +45084,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>530</v>
       </c>
@@ -45078,7 +45113,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>532</v>
       </c>
@@ -45107,7 +45142,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>534</v>
       </c>
@@ -45136,7 +45171,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>536</v>
       </c>
@@ -45165,7 +45200,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>538</v>
       </c>
@@ -45194,7 +45229,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>540</v>
       </c>
@@ -45223,7 +45258,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>542</v>
       </c>
@@ -45252,7 +45287,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>544</v>
       </c>
@@ -45281,7 +45316,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>546</v>
       </c>
@@ -45310,7 +45345,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>548</v>
       </c>
@@ -45339,7 +45374,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>550</v>
       </c>
@@ -45368,7 +45403,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>552</v>
       </c>
@@ -45397,7 +45432,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>554</v>
       </c>
@@ -45426,7 +45461,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>556</v>
       </c>
@@ -45455,7 +45490,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>558</v>
       </c>
@@ -45484,7 +45519,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>560</v>
       </c>
@@ -45513,7 +45548,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>562</v>
       </c>
@@ -45542,7 +45577,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>564</v>
       </c>
@@ -45571,7 +45606,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>566</v>
       </c>
@@ -45600,7 +45635,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>568</v>
       </c>
@@ -45629,7 +45664,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>570</v>
       </c>
@@ -45658,7 +45693,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>572</v>
       </c>
@@ -45687,7 +45722,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>574</v>
       </c>
@@ -45716,7 +45751,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>576</v>
       </c>
@@ -45745,7 +45780,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>578</v>
       </c>
@@ -45774,7 +45809,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>580</v>
       </c>
@@ -45803,7 +45838,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>582</v>
       </c>
@@ -45832,7 +45867,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>584</v>
       </c>
@@ -45861,7 +45896,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>586</v>
       </c>
@@ -45890,7 +45925,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>588</v>
       </c>
@@ -45919,7 +45954,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>590</v>
       </c>
@@ -45948,7 +45983,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>592</v>
       </c>
@@ -45977,7 +46012,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>594</v>
       </c>
@@ -46006,7 +46041,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>596</v>
       </c>
@@ -46035,7 +46070,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>598</v>
       </c>
@@ -46064,7 +46099,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>600</v>
       </c>
@@ -46093,7 +46128,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>602</v>
       </c>
@@ -46122,7 +46157,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>605</v>
       </c>
@@ -46151,7 +46186,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>608</v>
       </c>
@@ -46180,7 +46215,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>611</v>
       </c>
@@ -46209,7 +46244,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>613</v>
       </c>
@@ -46238,7 +46273,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>615</v>
       </c>
@@ -46267,7 +46302,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>617</v>
       </c>
@@ -46296,7 +46331,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>619</v>
       </c>
@@ -46325,7 +46360,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>621</v>
       </c>
@@ -46354,7 +46389,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>623</v>
       </c>
@@ -46383,7 +46418,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>625</v>
       </c>
@@ -46412,7 +46447,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>627</v>
       </c>
@@ -46441,7 +46476,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>629</v>
       </c>
@@ -46470,7 +46505,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>631</v>
       </c>
@@ -46499,7 +46534,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>633</v>
       </c>
@@ -46528,7 +46563,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>635</v>
       </c>
@@ -46557,7 +46592,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>637</v>
       </c>
@@ -46586,7 +46621,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>639</v>
       </c>
@@ -46615,7 +46650,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>641</v>
       </c>
@@ -46644,7 +46679,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>643</v>
       </c>
@@ -46673,7 +46708,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>646</v>
       </c>
@@ -46702,7 +46737,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>648</v>
       </c>
@@ -46731,7 +46766,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>651</v>
       </c>
@@ -46760,7 +46795,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>653</v>
       </c>
@@ -46789,7 +46824,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>656</v>
       </c>
@@ -46818,7 +46853,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>658</v>
       </c>
@@ -46847,7 +46882,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>660</v>
       </c>
@@ -46876,7 +46911,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>662</v>
       </c>
@@ -46905,7 +46940,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>665</v>
       </c>
@@ -46934,7 +46969,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>667</v>
       </c>
@@ -46963,7 +46998,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>670</v>
       </c>
@@ -46992,7 +47027,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>672</v>
       </c>
@@ -47021,7 +47056,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>674</v>
       </c>
@@ -47050,7 +47085,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>676</v>
       </c>
@@ -47079,7 +47114,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>678</v>
       </c>
@@ -47108,7 +47143,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>680</v>
       </c>
@@ -47137,7 +47172,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>682</v>
       </c>
@@ -47166,7 +47201,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>684</v>
       </c>
@@ -47195,7 +47230,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>686</v>
       </c>
@@ -47224,7 +47259,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>688</v>
       </c>
@@ -47253,7 +47288,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>690</v>
       </c>
@@ -47282,7 +47317,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>692</v>
       </c>
@@ -47311,7 +47346,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>694</v>
       </c>
@@ -47340,7 +47375,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>696</v>
       </c>
@@ -47369,7 +47404,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>698</v>
       </c>
@@ -47398,7 +47433,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>699</v>
       </c>
@@ -47427,7 +47462,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>702</v>
       </c>
@@ -47456,7 +47491,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>704</v>
       </c>
@@ -47485,7 +47520,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>706</v>
       </c>
@@ -47514,7 +47549,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>709</v>
       </c>
@@ -47543,7 +47578,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>711</v>
       </c>
@@ -47572,7 +47607,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>713</v>
       </c>
@@ -47601,7 +47636,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>716</v>
       </c>
@@ -47630,7 +47665,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>718</v>
       </c>
@@ -47659,7 +47694,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>720</v>
       </c>
@@ -47688,7 +47723,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>722</v>
       </c>
@@ -47717,7 +47752,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>724</v>
       </c>
@@ -47746,7 +47781,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>726</v>
       </c>
@@ -47775,7 +47810,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>728</v>
       </c>
@@ -47804,7 +47839,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>730</v>
       </c>
@@ -47833,7 +47868,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>732</v>
       </c>
@@ -47862,7 +47897,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>734</v>
       </c>
@@ -47891,7 +47926,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>736</v>
       </c>
@@ -47920,7 +47955,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>738</v>
       </c>
@@ -47949,7 +47984,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>740</v>
       </c>
@@ -47978,7 +48013,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>742</v>
       </c>
@@ -48007,7 +48042,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>744</v>
       </c>
@@ -48036,7 +48071,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>746</v>
       </c>
@@ -48065,7 +48100,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>748</v>
       </c>
@@ -48094,7 +48129,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>751</v>
       </c>
@@ -48123,7 +48158,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>754</v>
       </c>
@@ -48152,7 +48187,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>756</v>
       </c>
@@ -48181,7 +48216,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>758</v>
       </c>
@@ -48210,7 +48245,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>760</v>
       </c>
@@ -48239,7 +48274,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>762</v>
       </c>
@@ -48268,7 +48303,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>765</v>
       </c>
@@ -48297,7 +48332,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>767</v>
       </c>
@@ -48326,7 +48361,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>769</v>
       </c>
@@ -48355,7 +48390,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>771</v>
       </c>
@@ -48384,7 +48419,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>773</v>
       </c>
@@ -48413,7 +48448,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>775</v>
       </c>
@@ -48442,7 +48477,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>777</v>
       </c>
@@ -48471,7 +48506,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>779</v>
       </c>
@@ -48500,7 +48535,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>781</v>
       </c>
@@ -48529,7 +48564,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>783</v>
       </c>
@@ -48558,7 +48593,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>785</v>
       </c>
@@ -48587,7 +48622,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>787</v>
       </c>
@@ -48616,7 +48651,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>789</v>
       </c>
@@ -48645,7 +48680,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>791</v>
       </c>
@@ -48674,7 +48709,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>794</v>
       </c>
@@ -48703,7 +48738,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>795</v>
       </c>
@@ -48732,7 +48767,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>797</v>
       </c>
@@ -48761,7 +48796,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>800</v>
       </c>
@@ -48790,7 +48825,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>802</v>
       </c>
@@ -48819,7 +48854,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>804</v>
       </c>
@@ -48848,7 +48883,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>806</v>
       </c>
@@ -48877,7 +48912,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>809</v>
       </c>
@@ -48906,7 +48941,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>811</v>
       </c>
@@ -48935,7 +48970,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>813</v>
       </c>
@@ -48964,7 +48999,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>816</v>
       </c>
@@ -48993,7 +49028,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>818</v>
       </c>
@@ -49022,7 +49057,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>820</v>
       </c>
@@ -49051,7 +49086,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>822</v>
       </c>
@@ -49080,7 +49115,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>824</v>
       </c>
@@ -49109,7 +49144,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>827</v>
       </c>
@@ -49138,7 +49173,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>829</v>
       </c>
@@ -49167,7 +49202,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>832</v>
       </c>
@@ -49196,7 +49231,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>834</v>
       </c>
@@ -49227,6 +49262,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>